--- a/Deliverables/BOM/LCSC_BOM (20 Board).xlsx
+++ b/Deliverables/BOM/LCSC_BOM (20 Board).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Melih-SoundSensor\Deliverables\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D037C7A-EABC-4440-A1A0-BEAAD76C9984}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{038FC5DF-5991-44DA-A786-1FE2FC949D4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{AFC0FE78-E96F-42A2-AF8C-545056944A72}"/>
+    <workbookView xWindow="21930" yWindow="3270" windowWidth="11790" windowHeight="15360" xr2:uid="{AFC0FE78-E96F-42A2-AF8C-545056944A72}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
   <si>
     <t xml:space="preserve">LCSC Part No </t>
   </si>
@@ -123,9 +123,6 @@
   </si>
   <si>
     <t>C98220</t>
-  </si>
-  <si>
-    <t>C2869734</t>
   </si>
   <si>
     <t>C86534</t>
@@ -166,7 +163,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -179,7 +176,7 @@
       <sz val="12"/>
       <color theme="0"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -200,13 +197,13 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -222,7 +219,7 @@
       <sz val="10"/>
       <color theme="0"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -353,7 +350,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -429,6 +426,9 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -744,30 +744,33 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3116EBE4-BCEC-4598-9483-FE6FBD387B38}">
-  <dimension ref="A1:C59"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:F58"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14.28515625" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="16" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.28515625" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15.75" thickBot="1">
+    <row r="1" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1"/>
       <c r="B1"/>
-    </row>
-    <row r="2" spans="1:3" ht="16.5" thickBot="1">
+      <c r="F1"/>
+    </row>
+    <row r="2" spans="1:6" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B2" s="15" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="15.75" thickBot="1">
+        <v>39</v>
+      </c>
+      <c r="F2"/>
+    </row>
+    <row r="3" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="25">
         <v>1</v>
       </c>
@@ -777,8 +780,9 @@
       <c r="C3" s="7">
         <v>100</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" ht="15.75" thickBot="1">
+      <c r="F3"/>
+    </row>
+    <row r="4" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="25">
         <v>2</v>
       </c>
@@ -788,8 +792,9 @@
       <c r="C4" s="7">
         <v>40</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" ht="15.75" thickBot="1">
+      <c r="F4"/>
+    </row>
+    <row r="5" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="25">
         <v>3</v>
       </c>
@@ -799,8 +804,9 @@
       <c r="C5" s="7">
         <v>400</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" ht="15.75" thickBot="1">
+      <c r="F5"/>
+    </row>
+    <row r="6" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="25">
         <v>4</v>
       </c>
@@ -810,8 +816,9 @@
       <c r="C6" s="7">
         <v>200</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" ht="15.75" thickBot="1">
+      <c r="F6"/>
+    </row>
+    <row r="7" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="25">
         <v>5</v>
       </c>
@@ -821,8 +828,9 @@
       <c r="C7" s="7">
         <v>100</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" ht="15.75" thickBot="1">
+      <c r="F7"/>
+    </row>
+    <row r="8" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="25">
         <v>6</v>
       </c>
@@ -832,8 +840,9 @@
       <c r="C8" s="7">
         <v>600</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" ht="15.75" thickBot="1">
+      <c r="F8"/>
+    </row>
+    <row r="9" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="25">
         <v>7</v>
       </c>
@@ -843,8 +852,9 @@
       <c r="C9" s="8">
         <v>30</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" ht="15.75" thickBot="1">
+      <c r="F9"/>
+    </row>
+    <row r="10" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="25">
         <v>8</v>
       </c>
@@ -854,8 +864,9 @@
       <c r="C10" s="8">
         <v>200</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" ht="15.75" thickBot="1">
+      <c r="F10"/>
+    </row>
+    <row r="11" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="25">
         <v>9</v>
       </c>
@@ -865,8 +876,9 @@
       <c r="C11" s="8">
         <v>350</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" ht="15.75" thickBot="1">
+      <c r="F11"/>
+    </row>
+    <row r="12" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="25">
         <v>10</v>
       </c>
@@ -876,8 +888,9 @@
       <c r="C12" s="8">
         <v>50</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" ht="15.75" thickBot="1">
+      <c r="F12"/>
+    </row>
+    <row r="13" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="25">
         <v>11</v>
       </c>
@@ -887,8 +900,9 @@
       <c r="C13" s="8">
         <v>100</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" ht="15.75" thickBot="1">
+      <c r="F13"/>
+    </row>
+    <row r="14" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="25">
         <v>12</v>
       </c>
@@ -898,8 +912,9 @@
       <c r="C14" s="8">
         <v>100</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" ht="15.75" thickBot="1">
+      <c r="F14"/>
+    </row>
+    <row r="15" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="25">
         <v>13</v>
       </c>
@@ -909,8 +924,9 @@
       <c r="C15" s="8">
         <v>50</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" ht="15.75" thickBot="1">
+      <c r="F15"/>
+    </row>
+    <row r="16" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="25">
         <v>14</v>
       </c>
@@ -920,8 +936,9 @@
       <c r="C16" s="8">
         <v>50</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" ht="15.75" thickBot="1">
+      <c r="F16"/>
+    </row>
+    <row r="17" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="25">
         <v>15</v>
       </c>
@@ -931,8 +948,9 @@
       <c r="C17" s="8">
         <v>50</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" ht="15.75" thickBot="1">
+      <c r="F17"/>
+    </row>
+    <row r="18" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="25">
         <v>16</v>
       </c>
@@ -942,8 +960,9 @@
       <c r="C18" s="8">
         <v>30</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" ht="15.75" thickBot="1">
+      <c r="F18"/>
+    </row>
+    <row r="19" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="25">
         <v>17</v>
       </c>
@@ -953,8 +972,9 @@
       <c r="C19" s="9">
         <v>50</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" ht="15.75" thickBot="1">
+      <c r="F19"/>
+    </row>
+    <row r="20" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="25">
         <v>18</v>
       </c>
@@ -964,8 +984,9 @@
       <c r="C20" s="8">
         <v>50</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" ht="15.75" thickBot="1">
+      <c r="F20"/>
+    </row>
+    <row r="21" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="25">
         <v>19</v>
       </c>
@@ -975,8 +996,9 @@
       <c r="C21" s="8">
         <v>50</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" ht="15.75" thickBot="1">
+      <c r="F21"/>
+    </row>
+    <row r="22" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="25">
         <v>20</v>
       </c>
@@ -986,8 +1008,9 @@
       <c r="C22" s="8">
         <v>30</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" ht="15.75" thickBot="1">
+      <c r="F22"/>
+    </row>
+    <row r="23" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="25">
         <v>21</v>
       </c>
@@ -997,8 +1020,9 @@
       <c r="C23" s="7">
         <v>30</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" ht="15.75" thickBot="1">
+      <c r="F23"/>
+    </row>
+    <row r="24" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="25">
         <v>22</v>
       </c>
@@ -1008,8 +1032,9 @@
       <c r="C24" s="10">
         <v>22</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" ht="15.75" thickBot="1">
+      <c r="F24"/>
+    </row>
+    <row r="25" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="25">
         <v>23</v>
       </c>
@@ -1019,8 +1044,9 @@
       <c r="C25" s="11">
         <v>45</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" ht="15.75" thickBot="1">
+      <c r="F25"/>
+    </row>
+    <row r="26" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="25">
         <v>24</v>
       </c>
@@ -1030,8 +1056,9 @@
       <c r="C26" s="7">
         <v>25</v>
       </c>
-    </row>
-    <row r="27" spans="1:3" ht="15.75" thickBot="1">
+      <c r="F26"/>
+    </row>
+    <row r="27" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="25">
         <v>25</v>
       </c>
@@ -1041,8 +1068,9 @@
       <c r="C27" s="12">
         <v>100</v>
       </c>
-    </row>
-    <row r="28" spans="1:3" ht="15.75" thickBot="1">
+      <c r="F27"/>
+    </row>
+    <row r="28" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="25">
         <v>26</v>
       </c>
@@ -1052,8 +1080,9 @@
       <c r="C28" s="12">
         <v>100</v>
       </c>
-    </row>
-    <row r="29" spans="1:3" ht="15.75" thickBot="1">
+      <c r="F28"/>
+    </row>
+    <row r="29" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="25">
         <v>27</v>
       </c>
@@ -1063,8 +1092,9 @@
       <c r="C29" s="12">
         <v>100</v>
       </c>
-    </row>
-    <row r="30" spans="1:3" ht="15.75" thickBot="1">
+      <c r="F29"/>
+    </row>
+    <row r="30" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="25">
         <v>28</v>
       </c>
@@ -1074,8 +1104,9 @@
       <c r="C30" s="12">
         <v>100</v>
       </c>
-    </row>
-    <row r="31" spans="1:3" ht="15.75" thickBot="1">
+      <c r="F30"/>
+    </row>
+    <row r="31" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="25">
         <v>29</v>
       </c>
@@ -1085,30 +1116,33 @@
       <c r="C31" s="12">
         <v>100</v>
       </c>
-    </row>
-    <row r="32" spans="1:3" ht="15.75" thickBot="1">
+      <c r="F31"/>
+    </row>
+    <row r="32" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="25">
         <v>30</v>
       </c>
-      <c r="B32" s="16" t="s">
+      <c r="B32" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="C32" s="11">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" ht="15.75" thickBot="1">
+      <c r="C32" s="9">
+        <v>21</v>
+      </c>
+      <c r="F32"/>
+    </row>
+    <row r="33" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="25">
         <v>31</v>
       </c>
-      <c r="B33" s="19" t="s">
+      <c r="B33" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="C33" s="9">
+      <c r="C33" s="8">
         <v>21</v>
       </c>
-    </row>
-    <row r="34" spans="1:3" ht="15.75" thickBot="1">
+      <c r="F33"/>
+    </row>
+    <row r="34" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="25">
         <v>32</v>
       </c>
@@ -1118,41 +1152,45 @@
       <c r="C34" s="8">
         <v>21</v>
       </c>
-    </row>
-    <row r="35" spans="1:3" ht="15.75" thickBot="1">
+      <c r="F34"/>
+    </row>
+    <row r="35" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="25">
         <v>33</v>
       </c>
-      <c r="B35" s="20" t="s">
+      <c r="B35" s="21" t="s">
         <v>33</v>
       </c>
       <c r="C35" s="8">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" ht="15.75" thickBot="1">
+        <v>30</v>
+      </c>
+      <c r="F35"/>
+    </row>
+    <row r="36" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="25">
         <v>34</v>
       </c>
-      <c r="B36" s="21" t="s">
+      <c r="B36" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="C36" s="8">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" ht="15.75" thickBot="1">
+      <c r="C36" s="13">
+        <v>50</v>
+      </c>
+      <c r="F36"/>
+    </row>
+    <row r="37" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="25">
         <v>35</v>
       </c>
-      <c r="B37" s="22" t="s">
+      <c r="B37" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="C37" s="13">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" ht="15.75" thickBot="1">
+      <c r="C37" s="7">
+        <v>30</v>
+      </c>
+      <c r="F37"/>
+    </row>
+    <row r="38" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="25">
         <v>36</v>
       </c>
@@ -1160,100 +1198,106 @@
         <v>36</v>
       </c>
       <c r="C38" s="7">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" ht="15.75" thickBot="1">
+        <v>50</v>
+      </c>
+      <c r="F38"/>
+    </row>
+    <row r="39" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="25">
         <v>37</v>
       </c>
-      <c r="B39" s="21" t="s">
+      <c r="B39" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="C39" s="7">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" ht="15.75" thickBot="1">
-      <c r="A40" s="25">
+      <c r="C39" s="11">
+        <v>25</v>
+      </c>
+      <c r="F39"/>
+    </row>
+    <row r="40" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="6">
         <v>38</v>
       </c>
-      <c r="B40" s="23" t="s">
+      <c r="B40" s="24" t="s">
         <v>38</v>
       </c>
-      <c r="C40" s="11">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" ht="15.75" thickBot="1">
-      <c r="A41" s="6">
-        <v>39</v>
-      </c>
-      <c r="B41" s="24" t="s">
-        <v>39</v>
-      </c>
-      <c r="C41" s="14">
+      <c r="C40" s="14">
         <v>40</v>
       </c>
-    </row>
-    <row r="42" spans="1:3">
+      <c r="F40"/>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41"/>
+      <c r="B41" s="1"/>
+      <c r="C41" s="1"/>
+      <c r="F41"/>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42"/>
-      <c r="B42" s="1"/>
       <c r="C42" s="1"/>
-    </row>
-    <row r="43" spans="1:3">
+      <c r="F42"/>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43"/>
       <c r="C43" s="1"/>
-    </row>
-    <row r="44" spans="1:3">
+      <c r="F43"/>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44"/>
       <c r="C44" s="1"/>
-    </row>
-    <row r="45" spans="1:3">
+      <c r="F44"/>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45"/>
-      <c r="C45" s="1"/>
-    </row>
-    <row r="46" spans="1:3">
+      <c r="F45"/>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46"/>
-    </row>
-    <row r="47" spans="1:3">
+      <c r="F46"/>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47"/>
-    </row>
-    <row r="48" spans="1:3">
+      <c r="F47"/>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48"/>
-    </row>
-    <row r="49" spans="1:2">
+      <c r="F48"/>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49"/>
-    </row>
-    <row r="50" spans="1:2">
+      <c r="F49"/>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50"/>
-    </row>
-    <row r="51" spans="1:2">
+      <c r="F50"/>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51"/>
-    </row>
-    <row r="52" spans="1:2">
+      <c r="F51"/>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52"/>
-    </row>
-    <row r="53" spans="1:2">
+      <c r="F52"/>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53"/>
     </row>
-    <row r="54" spans="1:2">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54"/>
     </row>
-    <row r="55" spans="1:2">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55"/>
     </row>
-    <row r="56" spans="1:2">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56"/>
     </row>
-    <row r="57" spans="1:2">
-      <c r="A57"/>
-    </row>
-    <row r="58" spans="1:2">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B57" s="3"/>
+      <c r="F57" s="26"/>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B58" s="3"/>
-    </row>
-    <row r="59" spans="1:2">
-      <c r="B59" s="3"/>
+      <c r="F58" s="26"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Deliverables/BOM/LCSC_BOM (20 Board).xlsx
+++ b/Deliverables/BOM/LCSC_BOM (20 Board).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Melih-SoundSensor\Deliverables\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{038FC5DF-5991-44DA-A786-1FE2FC949D4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A09A2D4-204A-4036-979D-FF4F2BA83AC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="21930" yWindow="3270" windowWidth="11790" windowHeight="15360" xr2:uid="{AFC0FE78-E96F-42A2-AF8C-545056944A72}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{AFC0FE78-E96F-42A2-AF8C-545056944A72}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
   <si>
     <t xml:space="preserve">LCSC Part No </t>
   </si>
@@ -157,6 +157,9 @@
   </si>
   <si>
     <t>S. No.</t>
+  </si>
+  <si>
+    <t>C14677</t>
   </si>
 </sst>
 </file>
@@ -243,7 +246,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -346,11 +349,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -367,9 +381,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -429,6 +440,12 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -744,7 +761,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3116EBE4-BCEC-4598-9483-FE6FBD387B38}">
-  <dimension ref="A1:F58"/>
+  <dimension ref="A1:F59"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="2" bestFit="1" customWidth="1"/>
@@ -762,7 +779,7 @@
       <c r="A2" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="14" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="4" t="s">
@@ -771,371 +788,371 @@
       <c r="F2"/>
     </row>
     <row r="3" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="25">
+      <c r="A3" s="24">
         <v>1</v>
       </c>
-      <c r="B3" s="16" t="s">
+      <c r="B3" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="7">
+      <c r="C3" s="6">
         <v>100</v>
       </c>
       <c r="F3"/>
     </row>
     <row r="4" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="25">
+      <c r="A4" s="24">
         <v>2</v>
       </c>
-      <c r="B4" s="16" t="s">
+      <c r="B4" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="7">
+      <c r="C4" s="6">
         <v>40</v>
       </c>
       <c r="F4"/>
     </row>
     <row r="5" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="25">
+      <c r="A5" s="24">
         <v>3</v>
       </c>
-      <c r="B5" s="16" t="s">
+      <c r="B5" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="7">
+      <c r="C5" s="6">
         <v>400</v>
       </c>
       <c r="F5"/>
     </row>
     <row r="6" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="25">
+      <c r="A6" s="24">
         <v>4</v>
       </c>
-      <c r="B6" s="16" t="s">
+      <c r="B6" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="7">
+      <c r="C6" s="6">
         <v>200</v>
       </c>
       <c r="F6"/>
     </row>
     <row r="7" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="25">
+      <c r="A7" s="24">
         <v>5</v>
       </c>
-      <c r="B7" s="16" t="s">
+      <c r="B7" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="7">
+      <c r="C7" s="6">
         <v>100</v>
       </c>
       <c r="F7"/>
     </row>
     <row r="8" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="25">
+      <c r="A8" s="24">
         <v>6</v>
       </c>
-      <c r="B8" s="16" t="s">
+      <c r="B8" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="7">
+      <c r="C8" s="6">
         <v>600</v>
       </c>
       <c r="F8"/>
     </row>
     <row r="9" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="25">
+      <c r="A9" s="24">
         <v>7</v>
       </c>
-      <c r="B9" s="17" t="s">
+      <c r="B9" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="8">
+      <c r="C9" s="7">
         <v>30</v>
       </c>
       <c r="F9"/>
     </row>
     <row r="10" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="25">
+      <c r="A10" s="24">
         <v>8</v>
       </c>
-      <c r="B10" s="16" t="s">
+      <c r="B10" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="8">
+      <c r="C10" s="7">
         <v>200</v>
       </c>
       <c r="F10"/>
     </row>
     <row r="11" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="25">
+      <c r="A11" s="24">
         <v>9</v>
       </c>
-      <c r="B11" s="16" t="s">
+      <c r="B11" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="8">
+      <c r="C11" s="7">
         <v>350</v>
       </c>
       <c r="F11"/>
     </row>
     <row r="12" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="25">
+      <c r="A12" s="24">
         <v>10</v>
       </c>
-      <c r="B12" s="16" t="s">
+      <c r="B12" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="8">
+      <c r="C12" s="7">
         <v>50</v>
       </c>
       <c r="F12"/>
     </row>
     <row r="13" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="25">
+      <c r="A13" s="24">
         <v>11</v>
       </c>
-      <c r="B13" s="16" t="s">
+      <c r="B13" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="8">
+      <c r="C13" s="7">
         <v>100</v>
       </c>
       <c r="F13"/>
     </row>
     <row r="14" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="25">
+      <c r="A14" s="24">
         <v>12</v>
       </c>
-      <c r="B14" s="16" t="s">
+      <c r="B14" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="8">
+      <c r="C14" s="7">
         <v>100</v>
       </c>
       <c r="F14"/>
     </row>
     <row r="15" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="25">
+      <c r="A15" s="24">
         <v>13</v>
       </c>
-      <c r="B15" s="16" t="s">
+      <c r="B15" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="C15" s="8">
+      <c r="C15" s="7">
         <v>50</v>
       </c>
       <c r="F15"/>
     </row>
     <row r="16" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="25">
+      <c r="A16" s="24">
         <v>14</v>
       </c>
-      <c r="B16" s="16" t="s">
+      <c r="B16" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="C16" s="8">
+      <c r="C16" s="7">
         <v>50</v>
       </c>
       <c r="F16"/>
     </row>
     <row r="17" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="25">
+      <c r="A17" s="24">
         <v>15</v>
       </c>
-      <c r="B17" s="16" t="s">
+      <c r="B17" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="C17" s="8">
+      <c r="C17" s="7">
         <v>50</v>
       </c>
       <c r="F17"/>
     </row>
     <row r="18" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="25">
+      <c r="A18" s="24">
         <v>16</v>
       </c>
-      <c r="B18" s="16" t="s">
+      <c r="B18" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="C18" s="8">
+      <c r="C18" s="7">
         <v>30</v>
       </c>
       <c r="F18"/>
     </row>
     <row r="19" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="25">
+      <c r="A19" s="24">
         <v>17</v>
       </c>
-      <c r="B19" s="16" t="s">
+      <c r="B19" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="C19" s="9">
+      <c r="C19" s="8">
         <v>50</v>
       </c>
       <c r="F19"/>
     </row>
     <row r="20" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="25">
+      <c r="A20" s="24">
         <v>18</v>
       </c>
-      <c r="B20" s="16" t="s">
+      <c r="B20" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="C20" s="8">
+      <c r="C20" s="7">
         <v>50</v>
       </c>
       <c r="F20"/>
     </row>
     <row r="21" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="25">
+      <c r="A21" s="24">
         <v>19</v>
       </c>
-      <c r="B21" s="16" t="s">
+      <c r="B21" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="C21" s="8">
+      <c r="C21" s="7">
         <v>50</v>
       </c>
       <c r="F21"/>
     </row>
     <row r="22" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="25">
+      <c r="A22" s="24">
         <v>20</v>
       </c>
-      <c r="B22" s="16" t="s">
+      <c r="B22" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="C22" s="8">
+      <c r="C22" s="7">
         <v>30</v>
       </c>
       <c r="F22"/>
     </row>
     <row r="23" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="25">
+      <c r="A23" s="24">
         <v>21</v>
       </c>
-      <c r="B23" s="16" t="s">
+      <c r="B23" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="C23" s="7">
+      <c r="C23" s="6">
         <v>30</v>
       </c>
       <c r="F23"/>
     </row>
     <row r="24" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="25">
+      <c r="A24" s="24">
         <v>22</v>
       </c>
-      <c r="B24" s="18" t="s">
+      <c r="B24" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="C24" s="10">
+      <c r="C24" s="9">
         <v>22</v>
       </c>
       <c r="F24"/>
     </row>
     <row r="25" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="25">
+      <c r="A25" s="24">
         <v>23</v>
       </c>
-      <c r="B25" s="16" t="s">
+      <c r="B25" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="C25" s="11">
+      <c r="C25" s="10">
         <v>45</v>
       </c>
       <c r="F25"/>
     </row>
     <row r="26" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="25">
+      <c r="A26" s="24">
         <v>24</v>
       </c>
-      <c r="B26" s="16" t="s">
+      <c r="B26" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="C26" s="7">
+      <c r="C26" s="6">
         <v>25</v>
       </c>
       <c r="F26"/>
     </row>
     <row r="27" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="25">
+      <c r="A27" s="24">
         <v>25</v>
       </c>
-      <c r="B27" s="16" t="s">
+      <c r="B27" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="C27" s="12">
+      <c r="C27" s="11">
         <v>100</v>
       </c>
       <c r="F27"/>
     </row>
     <row r="28" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="25">
+      <c r="A28" s="24">
         <v>26</v>
       </c>
-      <c r="B28" s="16" t="s">
+      <c r="B28" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="C28" s="12">
+      <c r="C28" s="11">
         <v>100</v>
       </c>
       <c r="F28"/>
     </row>
     <row r="29" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="25">
+      <c r="A29" s="24">
         <v>27</v>
       </c>
-      <c r="B29" s="16" t="s">
+      <c r="B29" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="C29" s="12">
+      <c r="C29" s="11">
         <v>100</v>
       </c>
       <c r="F29"/>
     </row>
     <row r="30" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="25">
+      <c r="A30" s="24">
         <v>28</v>
       </c>
-      <c r="B30" s="16" t="s">
+      <c r="B30" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="C30" s="12">
+      <c r="C30" s="11">
         <v>100</v>
       </c>
       <c r="F30"/>
     </row>
     <row r="31" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="25">
+      <c r="A31" s="24">
         <v>29</v>
       </c>
-      <c r="B31" s="16" t="s">
+      <c r="B31" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="C31" s="12">
+      <c r="C31" s="11">
         <v>100</v>
       </c>
       <c r="F31"/>
     </row>
     <row r="32" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="25">
+      <c r="A32" s="24">
         <v>30</v>
       </c>
-      <c r="B32" s="19" t="s">
+      <c r="B32" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="C32" s="11">
+        <v>100</v>
+      </c>
+      <c r="F32"/>
+    </row>
+    <row r="33" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="24">
+        <v>31</v>
+      </c>
+      <c r="B33" s="18" t="s">
         <v>30</v>
-      </c>
-      <c r="C32" s="9">
-        <v>21</v>
-      </c>
-      <c r="F32"/>
-    </row>
-    <row r="33" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="25">
-        <v>31</v>
-      </c>
-      <c r="B33" s="20" t="s">
-        <v>31</v>
       </c>
       <c r="C33" s="8">
         <v>21</v>
@@ -1143,97 +1160,104 @@
       <c r="F33"/>
     </row>
     <row r="34" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="25">
+      <c r="A34" s="24">
         <v>32</v>
       </c>
-      <c r="B34" s="20" t="s">
+      <c r="B34" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="C34" s="7">
+        <v>21</v>
+      </c>
+      <c r="F34"/>
+    </row>
+    <row r="35" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="24">
+        <v>33</v>
+      </c>
+      <c r="B35" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="C34" s="8">
+      <c r="C35" s="7">
         <v>21</v>
       </c>
-      <c r="F34"/>
-    </row>
-    <row r="35" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="25">
+      <c r="F35"/>
+    </row>
+    <row r="36" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="24">
+        <v>34</v>
+      </c>
+      <c r="B36" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="B35" s="21" t="s">
-        <v>33</v>
-      </c>
-      <c r="C35" s="8">
+      <c r="C36" s="7">
         <v>30</v>
       </c>
-      <c r="F35"/>
-    </row>
-    <row r="36" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="25">
+      <c r="F36"/>
+    </row>
+    <row r="37" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="24">
+        <v>35</v>
+      </c>
+      <c r="B37" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="B36" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="C36" s="13">
+      <c r="C37" s="12">
         <v>50</v>
       </c>
-      <c r="F36"/>
-    </row>
-    <row r="37" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="25">
+      <c r="F37"/>
+    </row>
+    <row r="38" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="24">
+        <v>36</v>
+      </c>
+      <c r="B38" s="20" t="s">
         <v>35</v>
       </c>
-      <c r="B37" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="C37" s="7">
+      <c r="C38" s="6">
         <v>30</v>
       </c>
-      <c r="F37"/>
-    </row>
-    <row r="38" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="25">
+      <c r="F38"/>
+    </row>
+    <row r="39" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="24">
+        <v>37</v>
+      </c>
+      <c r="B39" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="B38" s="21" t="s">
-        <v>36</v>
-      </c>
-      <c r="C38" s="7">
+      <c r="C39" s="6">
         <v>50</v>
       </c>
-      <c r="F38"/>
-    </row>
-    <row r="39" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="25">
+      <c r="F39"/>
+    </row>
+    <row r="40" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="24">
+        <v>38</v>
+      </c>
+      <c r="B40" s="22" t="s">
         <v>37</v>
       </c>
-      <c r="B39" s="23" t="s">
-        <v>37</v>
-      </c>
-      <c r="C39" s="11">
+      <c r="C40" s="10">
         <v>25</v>
       </c>
-      <c r="F39"/>
-    </row>
-    <row r="40" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="6">
+      <c r="F40"/>
+    </row>
+    <row r="41" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="27">
+        <v>39</v>
+      </c>
+      <c r="B41" s="23" t="s">
         <v>38</v>
       </c>
-      <c r="B40" s="24" t="s">
-        <v>38</v>
-      </c>
-      <c r="C40" s="14">
+      <c r="C41" s="13">
         <v>40</v>
       </c>
-      <c r="F40"/>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41"/>
-      <c r="B41" s="1"/>
-      <c r="C41" s="1"/>
       <c r="F41"/>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42"/>
+      <c r="B42" s="1"/>
       <c r="C42" s="1"/>
       <c r="F42"/>
     </row>
@@ -1249,6 +1273,7 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45"/>
+      <c r="C45" s="1"/>
       <c r="F45"/>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
@@ -1281,6 +1306,7 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53"/>
+      <c r="F53"/>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54"/>
@@ -1292,12 +1318,15 @@
       <c r="A56"/>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B57" s="3"/>
-      <c r="F57" s="26"/>
+      <c r="A57"/>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B58" s="3"/>
-      <c r="F58" s="26"/>
+      <c r="F58" s="25"/>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B59" s="3"/>
+      <c r="F59" s="25"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
